--- a/Excel/SevenDayConfig.xlsx
+++ b/Excel/SevenDayConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="67">
   <si>
     <t>#</t>
   </si>
@@ -107,7 +107,7 @@
     <t>魂环碎片</t>
   </si>
   <si>
-    <t>兑换书页100个</t>
+    <t>兑换书页200个</t>
   </si>
   <si>
     <t>书页</t>
@@ -125,6 +125,9 @@
     <t>BOSS挑战卷</t>
   </si>
   <si>
+    <t>兑换专属自选套</t>
+  </si>
+  <si>
     <t>兑换战神时装包*1</t>
   </si>
   <si>
@@ -213,9 +216,6 @@
   </si>
   <si>
     <t>传世挑战卷</t>
-  </si>
-  <si>
-    <t>兑换专属自选套</t>
   </si>
   <si>
     <t>兑换专属之心*5</t>
@@ -1230,7 +1230,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L69"/>
+  <dimension ref="C1:L70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1565,7 +1565,7 @@
         <v>4006</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:11">
@@ -1626,38 +1626,38 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:11">
-      <c r="C17" s="1">
-        <v>100</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1">
-        <v>200</v>
-      </c>
-      <c r="F17" s="1">
-        <v>40</v>
-      </c>
-      <c r="G17" s="1" t="s">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
+        <v>7</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1000</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I17" s="1">
+      <c r="H16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="1">
         <v>4</v>
       </c>
-      <c r="J17" s="1">
-        <v>10</v>
-      </c>
-      <c r="K17" s="1">
+      <c r="J16" s="1">
+        <v>97</v>
+      </c>
+      <c r="K16" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:11">
       <c r="C18" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
@@ -1669,16 +1669,16 @@
         <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="I18" s="1">
         <v>4</v>
       </c>
       <c r="J18" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K18" s="1">
         <v>1</v>
@@ -1686,7 +1686,7 @@
     </row>
     <row r="19" customHeight="1" spans="3:11">
       <c r="C19" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
@@ -1698,16 +1698,16 @@
         <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I19" s="1">
         <v>4</v>
       </c>
       <c r="J19" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K19" s="1">
         <v>1</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="20" customHeight="1" spans="3:11">
       <c r="C20" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D20" s="1">
         <v>2</v>
@@ -1727,16 +1727,16 @@
         <v>40</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I20" s="1">
         <v>4</v>
       </c>
-      <c r="J20" s="4">
-        <v>15</v>
+      <c r="J20" s="1">
+        <v>12</v>
       </c>
       <c r="K20" s="1">
         <v>1</v>
@@ -1744,7 +1744,7 @@
     </row>
     <row r="21" customHeight="1" spans="3:11">
       <c r="C21" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -1756,16 +1756,16 @@
         <v>40</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="I21" s="1">
         <v>4</v>
       </c>
       <c r="J21" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K21" s="1">
         <v>1</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="22" customHeight="1" spans="3:11">
       <c r="C22" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
@@ -1785,16 +1785,16 @@
         <v>40</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="I22" s="1">
         <v>4</v>
       </c>
       <c r="J22" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K22" s="1">
         <v>1</v>
@@ -1802,65 +1802,65 @@
     </row>
     <row r="23" customHeight="1" spans="3:11">
       <c r="C23" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D23" s="1">
         <v>2</v>
       </c>
       <c r="E23" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F23" s="1">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="I23" s="1">
-        <v>5</v>
-      </c>
-      <c r="J23" s="1">
-        <v>4002</v>
+        <v>4</v>
+      </c>
+      <c r="J23" s="4">
+        <v>17</v>
       </c>
       <c r="K23" s="1">
-        <v>1000000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:11">
       <c r="C24" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D24" s="1">
         <v>2</v>
       </c>
       <c r="E24" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F24" s="1">
         <v>15</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I24" s="1">
         <v>5</v>
       </c>
       <c r="J24" s="1">
-        <v>4007</v>
+        <v>4002</v>
       </c>
       <c r="K24" s="1">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:11">
       <c r="C25" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D25" s="1">
         <v>2</v>
@@ -1872,16 +1872,16 @@
         <v>15</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I25" s="1">
         <v>5</v>
       </c>
       <c r="J25" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K25" s="1">
         <v>1000</v>
@@ -1889,97 +1889,97 @@
     </row>
     <row r="26" customHeight="1" spans="3:11">
       <c r="C26" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D26" s="1">
         <v>2</v>
       </c>
       <c r="E26" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F26" s="1">
         <v>15</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I26" s="1">
         <v>5</v>
       </c>
       <c r="J26" s="1">
-        <v>4001</v>
+        <v>4101</v>
       </c>
       <c r="K26" s="1">
-        <v>500000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:11">
       <c r="C27" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
       </c>
       <c r="E27" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F27" s="1">
         <v>15</v>
       </c>
       <c r="G27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I27" s="1">
+        <v>5</v>
+      </c>
+      <c r="J27" s="1">
+        <v>4001</v>
+      </c>
+      <c r="K27" s="1">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:11">
+      <c r="C28" s="1">
+        <v>110</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1">
+        <v>100</v>
+      </c>
+      <c r="F28" s="1">
+        <v>15</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I27" s="1">
-        <v>5</v>
-      </c>
-      <c r="J27" s="1">
+      <c r="I28" s="1">
+        <v>5</v>
+      </c>
+      <c r="J28" s="1">
         <v>4006</v>
       </c>
-      <c r="K27" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="10:10">
-      <c r="J28" s="4"/>
-    </row>
-    <row r="29" customHeight="1" spans="3:11">
-      <c r="C29" s="1">
+      <c r="K28" s="1">
         <v>200</v>
       </c>
-      <c r="D29" s="1">
-        <v>3</v>
-      </c>
-      <c r="E29" s="1">
-        <v>200</v>
-      </c>
-      <c r="F29" s="1">
-        <v>40</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I29" s="1">
-        <v>11</v>
-      </c>
-      <c r="J29" s="1">
-        <v>1999995</v>
-      </c>
-      <c r="K29" s="1">
-        <v>1</v>
-      </c>
+    </row>
+    <row r="29" customHeight="1" spans="10:10">
+      <c r="J29" s="4"/>
     </row>
     <row r="30" customHeight="1" spans="3:11">
       <c r="C30" s="1">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D30" s="1">
         <v>3</v>
@@ -1991,16 +1991,16 @@
         <v>40</v>
       </c>
       <c r="G30" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="I30" s="1">
         <v>11</v>
       </c>
       <c r="J30" s="1">
-        <v>1999996</v>
+        <v>1999995</v>
       </c>
       <c r="K30" s="1">
         <v>1</v>
@@ -2008,7 +2008,7 @@
     </row>
     <row r="31" customHeight="1" spans="3:11">
       <c r="C31" s="1">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D31" s="1">
         <v>3</v>
@@ -2020,16 +2020,16 @@
         <v>40</v>
       </c>
       <c r="G31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="I31" s="1">
         <v>11</v>
       </c>
       <c r="J31" s="1">
-        <v>1999997</v>
+        <v>1999996</v>
       </c>
       <c r="K31" s="1">
         <v>1</v>
@@ -2037,7 +2037,7 @@
     </row>
     <row r="32" customHeight="1" spans="3:11">
       <c r="C32" s="1">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D32" s="1">
         <v>3</v>
@@ -2049,16 +2049,16 @@
         <v>40</v>
       </c>
       <c r="G32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="I32" s="1">
         <v>11</v>
       </c>
       <c r="J32" s="1">
-        <v>1999994</v>
+        <v>1999997</v>
       </c>
       <c r="K32" s="1">
         <v>1</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="33" customHeight="1" spans="3:11">
       <c r="C33" s="1">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D33" s="1">
         <v>3</v>
@@ -2078,16 +2078,16 @@
         <v>40</v>
       </c>
       <c r="G33" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="I33" s="1">
         <v>11</v>
       </c>
       <c r="J33" s="1">
-        <v>1999993</v>
+        <v>1999994</v>
       </c>
       <c r="K33" s="1">
         <v>1</v>
@@ -2095,65 +2095,65 @@
     </row>
     <row r="34" customHeight="1" spans="3:11">
       <c r="C34" s="1">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D34" s="1">
         <v>3</v>
       </c>
       <c r="E34" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F34" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="I34" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J34" s="1">
-        <v>4002</v>
+        <v>1999993</v>
       </c>
       <c r="K34" s="1">
-        <v>1000000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:11">
       <c r="C35" s="1">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D35" s="1">
         <v>3</v>
       </c>
       <c r="E35" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F35" s="1">
         <v>20</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I35" s="1">
         <v>5</v>
       </c>
       <c r="J35" s="1">
-        <v>4007</v>
+        <v>4002</v>
       </c>
       <c r="K35" s="1">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:11">
       <c r="C36" s="1">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D36" s="1">
         <v>3</v>
@@ -2165,16 +2165,16 @@
         <v>20</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I36" s="1">
         <v>5</v>
       </c>
       <c r="J36" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K36" s="1">
         <v>1000</v>
@@ -2182,152 +2182,152 @@
     </row>
     <row r="37" customHeight="1" spans="3:11">
       <c r="C37" s="1">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D37" s="1">
         <v>3</v>
       </c>
       <c r="E37" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F37" s="1">
         <v>20</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I37" s="1">
         <v>5</v>
       </c>
       <c r="J37" s="1">
-        <v>4001</v>
+        <v>4101</v>
       </c>
       <c r="K37" s="1">
-        <v>500000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:11">
       <c r="C38" s="1">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D38" s="1">
         <v>3</v>
       </c>
       <c r="E38" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F38" s="1">
         <v>20</v>
       </c>
       <c r="G38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I38" s="1">
+        <v>5</v>
+      </c>
+      <c r="J38" s="1">
+        <v>4001</v>
+      </c>
+      <c r="K38" s="1">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:11">
+      <c r="C39" s="1">
+        <v>209</v>
+      </c>
+      <c r="D39" s="1">
+        <v>3</v>
+      </c>
+      <c r="E39" s="1">
+        <v>100</v>
+      </c>
+      <c r="F39" s="1">
+        <v>20</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H39" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I38" s="1">
-        <v>5</v>
-      </c>
-      <c r="J38" s="1">
+      <c r="I39" s="1">
+        <v>5</v>
+      </c>
+      <c r="J39" s="1">
         <v>4006</v>
       </c>
-      <c r="K38" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C40" s="1">
+      <c r="K39" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C41" s="1">
         <v>300</v>
-      </c>
-      <c r="D40" s="1">
-        <v>4</v>
-      </c>
-      <c r="E40" s="1">
-        <v>10000</v>
-      </c>
-      <c r="F40" s="1">
-        <v>10</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I40" s="1">
-        <v>4</v>
-      </c>
-      <c r="J40" s="1">
-        <v>22</v>
-      </c>
-      <c r="K40" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:11">
-      <c r="C41" s="1">
-        <v>301</v>
       </c>
       <c r="D41" s="1">
         <v>4</v>
       </c>
       <c r="E41" s="1">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F41" s="1">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="I41" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J41" s="1">
-        <v>4002</v>
+        <v>22</v>
       </c>
       <c r="K41" s="1">
-        <v>1000000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:11">
       <c r="C42" s="1">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D42" s="1">
         <v>4</v>
       </c>
       <c r="E42" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F42" s="1">
         <v>25</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I42" s="1">
         <v>5</v>
       </c>
       <c r="J42" s="1">
-        <v>4007</v>
+        <v>4002</v>
       </c>
       <c r="K42" s="1">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:11">
       <c r="C43" s="1">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D43" s="1">
         <v>4</v>
@@ -2339,16 +2339,16 @@
         <v>25</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I43" s="1">
         <v>5</v>
       </c>
       <c r="J43" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K43" s="1">
         <v>1000</v>
@@ -2356,152 +2356,152 @@
     </row>
     <row r="44" customHeight="1" spans="3:11">
       <c r="C44" s="1">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D44" s="1">
         <v>4</v>
       </c>
       <c r="E44" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F44" s="1">
         <v>25</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I44" s="1">
         <v>5</v>
       </c>
       <c r="J44" s="1">
-        <v>4001</v>
+        <v>4101</v>
       </c>
       <c r="K44" s="1">
-        <v>500000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:11">
       <c r="C45" s="1">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D45" s="1">
         <v>4</v>
       </c>
       <c r="E45" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F45" s="1">
         <v>25</v>
       </c>
       <c r="G45" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I45" s="1">
+        <v>5</v>
+      </c>
+      <c r="J45" s="1">
+        <v>4001</v>
+      </c>
+      <c r="K45" s="1">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:11">
+      <c r="C46" s="1">
+        <v>305</v>
+      </c>
+      <c r="D46" s="1">
+        <v>4</v>
+      </c>
+      <c r="E46" s="1">
+        <v>100</v>
+      </c>
+      <c r="F46" s="1">
+        <v>25</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I45" s="1">
-        <v>5</v>
-      </c>
-      <c r="J45" s="1">
+      <c r="I46" s="1">
+        <v>5</v>
+      </c>
+      <c r="J46" s="1">
         <v>4006</v>
       </c>
-      <c r="K45" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C47" s="1">
+      <c r="K46" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C48" s="1">
         <v>400</v>
       </c>
-      <c r="D47" s="1">
-        <v>5</v>
-      </c>
-      <c r="E47" s="1">
+      <c r="D48" s="1">
+        <v>5</v>
+      </c>
+      <c r="E48" s="1">
         <v>20000</v>
       </c>
-      <c r="F47" s="1">
-        <v>5</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H47" s="1" t="s">
+      <c r="F48" s="1">
+        <v>5</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I47" s="1">
+      <c r="H48" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I48" s="1">
         <v>4</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J48" s="1">
         <v>26</v>
       </c>
-      <c r="K47" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:11">
-      <c r="C48" s="1">
-        <v>401</v>
-      </c>
-      <c r="D48" s="1">
-        <v>5</v>
-      </c>
-      <c r="E48" s="1">
-        <v>500</v>
-      </c>
-      <c r="F48" s="1">
-        <v>30</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I48" s="1">
-        <v>5</v>
-      </c>
-      <c r="J48" s="1">
-        <v>4002</v>
-      </c>
       <c r="K48" s="1">
-        <v>1000000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:11">
       <c r="C49" s="1">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D49" s="1">
         <v>5</v>
       </c>
       <c r="E49" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F49" s="1">
         <v>30</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I49" s="1">
         <v>5</v>
       </c>
       <c r="J49" s="1">
-        <v>4007</v>
+        <v>4002</v>
       </c>
       <c r="K49" s="1">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:11">
       <c r="C50" s="1">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D50" s="1">
         <v>5</v>
@@ -2513,16 +2513,16 @@
         <v>30</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I50" s="1">
         <v>5</v>
       </c>
       <c r="J50" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K50" s="1">
         <v>1000</v>
@@ -2530,152 +2530,152 @@
     </row>
     <row r="51" customHeight="1" spans="3:11">
       <c r="C51" s="1">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D51" s="1">
         <v>5</v>
       </c>
       <c r="E51" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F51" s="1">
         <v>30</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I51" s="1">
         <v>5</v>
       </c>
       <c r="J51" s="1">
-        <v>4001</v>
+        <v>4101</v>
       </c>
       <c r="K51" s="1">
-        <v>500000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D52" s="1">
         <v>5</v>
       </c>
       <c r="E52" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F52" s="1">
         <v>30</v>
       </c>
       <c r="G52" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I52" s="1">
+        <v>5</v>
+      </c>
+      <c r="J52" s="1">
+        <v>4001</v>
+      </c>
+      <c r="K52" s="1">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:11">
+      <c r="C53" s="1">
+        <v>405</v>
+      </c>
+      <c r="D53" s="1">
+        <v>5</v>
+      </c>
+      <c r="E53" s="1">
+        <v>100</v>
+      </c>
+      <c r="F53" s="1">
+        <v>30</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="H53" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I52" s="1">
-        <v>5</v>
-      </c>
-      <c r="J52" s="1">
+      <c r="I53" s="1">
+        <v>5</v>
+      </c>
+      <c r="J53" s="1">
         <v>4006</v>
       </c>
-      <c r="K52" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C54" s="1">
+      <c r="K53" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C55" s="1">
         <v>500</v>
-      </c>
-      <c r="D54" s="1">
-        <v>6</v>
-      </c>
-      <c r="E54" s="1">
-        <v>50000</v>
-      </c>
-      <c r="F54" s="1">
-        <v>3</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="I54" s="1">
-        <v>4</v>
-      </c>
-      <c r="J54" s="1">
-        <v>24</v>
-      </c>
-      <c r="K54" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:11">
-      <c r="C55" s="1">
-        <v>501</v>
       </c>
       <c r="D55" s="1">
         <v>6</v>
       </c>
       <c r="E55" s="1">
-        <v>500</v>
+        <v>50000</v>
       </c>
       <c r="F55" s="1">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="I55" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J55" s="1">
-        <v>4002</v>
+        <v>24</v>
       </c>
       <c r="K55" s="1">
-        <v>1000000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:11">
       <c r="C56" s="1">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D56" s="1">
         <v>6</v>
       </c>
       <c r="E56" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F56" s="1">
         <v>35</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I56" s="1">
         <v>5</v>
       </c>
       <c r="J56" s="1">
-        <v>4007</v>
+        <v>4002</v>
       </c>
       <c r="K56" s="1">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:11">
       <c r="C57" s="1">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D57" s="1">
         <v>6</v>
@@ -2687,16 +2687,16 @@
         <v>35</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I57" s="1">
         <v>5</v>
       </c>
       <c r="J57" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K57" s="1">
         <v>1000</v>
@@ -2704,181 +2704,181 @@
     </row>
     <row r="58" customHeight="1" spans="3:11">
       <c r="C58" s="1">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D58" s="1">
         <v>6</v>
       </c>
       <c r="E58" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F58" s="1">
         <v>35</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I58" s="1">
         <v>5</v>
       </c>
       <c r="J58" s="1">
-        <v>4001</v>
+        <v>4101</v>
       </c>
       <c r="K58" s="1">
-        <v>500000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D59" s="1">
         <v>6</v>
       </c>
       <c r="E59" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F59" s="1">
         <v>35</v>
       </c>
       <c r="G59" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I59" s="1">
+        <v>5</v>
+      </c>
+      <c r="J59" s="1">
+        <v>4001</v>
+      </c>
+      <c r="K59" s="1">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:11">
+      <c r="C60" s="1">
+        <v>505</v>
+      </c>
+      <c r="D60" s="1">
+        <v>6</v>
+      </c>
+      <c r="E60" s="1">
+        <v>100</v>
+      </c>
+      <c r="F60" s="1">
+        <v>35</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="H60" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I59" s="1">
-        <v>5</v>
-      </c>
-      <c r="J59" s="1">
+      <c r="I60" s="1">
+        <v>5</v>
+      </c>
+      <c r="J60" s="1">
         <v>4006</v>
       </c>
-      <c r="K59" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:11">
-      <c r="C61" s="1">
+      <c r="K60" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:11">
+      <c r="C62" s="1">
         <v>600</v>
-      </c>
-      <c r="D61" s="1">
-        <v>7</v>
-      </c>
-      <c r="E61" s="1">
-        <v>300</v>
-      </c>
-      <c r="F61" s="1">
-        <v>88</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I61" s="1">
-        <v>9</v>
-      </c>
-      <c r="J61" s="1">
-        <v>4013</v>
-      </c>
-      <c r="K61" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C62" s="1">
-        <v>601</v>
       </c>
       <c r="D62" s="1">
         <v>7</v>
       </c>
       <c r="E62" s="1">
-        <v>30000</v>
+        <v>300</v>
       </c>
       <c r="F62" s="1">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>62</v>
       </c>
       <c r="I62" s="1">
+        <v>9</v>
+      </c>
+      <c r="J62" s="1">
+        <v>4013</v>
+      </c>
+      <c r="K62" s="1">
         <v>4</v>
       </c>
-      <c r="J62" s="1">
-        <v>98</v>
-      </c>
-      <c r="K62" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:11">
+    </row>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C63" s="1">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D63" s="1">
         <v>7</v>
       </c>
       <c r="E63" s="1">
-        <v>500</v>
+        <v>30000</v>
       </c>
       <c r="F63" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="I63" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J63" s="1">
-        <v>4002</v>
+        <v>98</v>
       </c>
       <c r="K63" s="1">
-        <v>1000000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:11">
       <c r="C64" s="1">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D64" s="1">
         <v>7</v>
       </c>
       <c r="E64" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F64" s="1">
         <v>50</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I64" s="1">
         <v>5</v>
       </c>
       <c r="J64" s="1">
-        <v>4007</v>
+        <v>4002</v>
       </c>
       <c r="K64" s="1">
-        <v>1000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:11">
       <c r="C65" s="1">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D65" s="1">
         <v>7</v>
@@ -2890,16 +2890,16 @@
         <v>50</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I65" s="1">
         <v>5</v>
       </c>
       <c r="J65" s="1">
-        <v>4101</v>
+        <v>4007</v>
       </c>
       <c r="K65" s="1">
         <v>1000</v>
@@ -2907,94 +2907,94 @@
     </row>
     <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D66" s="1">
         <v>7</v>
       </c>
       <c r="E66" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F66" s="1">
         <v>50</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I66" s="1">
         <v>5</v>
       </c>
       <c r="J66" s="1">
-        <v>4001</v>
+        <v>4101</v>
       </c>
       <c r="K66" s="1">
-        <v>500000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:11">
       <c r="C67" s="1">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D67" s="1">
         <v>7</v>
       </c>
       <c r="E67" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F67" s="1">
         <v>50</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I67" s="1">
         <v>5</v>
       </c>
       <c r="J67" s="1">
-        <v>4006</v>
+        <v>4001</v>
       </c>
       <c r="K67" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:11">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D68" s="1">
         <v>7</v>
       </c>
       <c r="E68" s="1">
-        <v>4000</v>
+        <v>100</v>
       </c>
       <c r="F68" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="I68" s="1">
         <v>5</v>
       </c>
       <c r="J68" s="1">
-        <v>4010</v>
+        <v>4006</v>
       </c>
       <c r="K68" s="1">
-        <v>5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C69" s="1">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D69" s="1">
         <v>7</v>
@@ -3003,21 +3003,50 @@
         <v>4000</v>
       </c>
       <c r="F69" s="1">
+        <v>100</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I69" s="1">
+        <v>5</v>
+      </c>
+      <c r="J69" s="1">
+        <v>4010</v>
+      </c>
+      <c r="K69" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C70" s="1">
+        <v>608</v>
+      </c>
+      <c r="D70" s="1">
+        <v>7</v>
+      </c>
+      <c r="E70" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F70" s="1">
         <v>40</v>
       </c>
-      <c r="G69" s="1" t="s">
+      <c r="G70" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="H70" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I69" s="1">
-        <v>5</v>
-      </c>
-      <c r="J69" s="1">
+      <c r="I70" s="1">
+        <v>5</v>
+      </c>
+      <c r="J70" s="1">
         <v>4102</v>
       </c>
-      <c r="K69" s="1">
+      <c r="K70" s="1">
         <v>20</v>
       </c>
     </row>

--- a/Excel/SevenDayConfig.xlsx
+++ b/Excel/SevenDayConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="68">
   <si>
     <t>#</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>兑换专属自选套</t>
+  </si>
+  <si>
+    <t>盾专属套</t>
   </si>
   <si>
     <t>兑换战神时装包*1</t>
@@ -1234,11 +1237,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.2545454545455" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1272727272727" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.8727272727273" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
@@ -1373,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -1515,7 +1518,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="1">
         <v>500</v>
@@ -1631,7 +1634,7 @@
         <v>11</v>
       </c>
       <c r="D16" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E16" s="1">
         <v>1000</v>
@@ -1643,7 +1646,7 @@
         <v>32</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I16" s="1">
         <v>4</v>
@@ -1669,10 +1672,10 @@
         <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I18" s="1">
         <v>4</v>
@@ -1698,10 +1701,10 @@
         <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I19" s="1">
         <v>4</v>
@@ -1727,10 +1730,10 @@
         <v>40</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I20" s="1">
         <v>4</v>
@@ -1756,10 +1759,10 @@
         <v>40</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I21" s="1">
         <v>4</v>
@@ -1785,10 +1788,10 @@
         <v>40</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I22" s="1">
         <v>4</v>
@@ -1814,10 +1817,10 @@
         <v>40</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I23" s="1">
         <v>4</v>
@@ -1991,10 +1994,10 @@
         <v>40</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I30" s="1">
         <v>11</v>
@@ -2020,10 +2023,10 @@
         <v>40</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I31" s="1">
         <v>11</v>
@@ -2049,10 +2052,10 @@
         <v>40</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I32" s="1">
         <v>11</v>
@@ -2078,10 +2081,10 @@
         <v>40</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I33" s="1">
         <v>11</v>
@@ -2107,10 +2110,10 @@
         <v>40</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I34" s="1">
         <v>11</v>
@@ -2281,10 +2284,10 @@
         <v>10</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I41" s="1">
         <v>4</v>
@@ -2455,10 +2458,10 @@
         <v>5</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I48" s="1">
         <v>4</v>
@@ -2629,10 +2632,10 @@
         <v>3</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I55" s="1">
         <v>4</v>
@@ -2803,10 +2806,10 @@
         <v>88</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I62" s="1">
         <v>9</v>
@@ -3006,10 +3009,10 @@
         <v>100</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I69" s="1">
         <v>5</v>
@@ -3035,10 +3038,10 @@
         <v>40</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I70" s="1">
         <v>5</v>

--- a/Excel/SevenDayConfig.xlsx
+++ b/Excel/SevenDayConfig.xlsx
@@ -131,40 +131,40 @@
     <t>盾专属套</t>
   </si>
   <si>
-    <t>兑换战神时装包*1</t>
-  </si>
-  <si>
-    <t>战神时装包</t>
-  </si>
-  <si>
-    <t>兑换恶魔时装包*1</t>
-  </si>
-  <si>
-    <t>恶魔时装包</t>
-  </si>
-  <si>
-    <t>兑换幽灵时装包*1</t>
-  </si>
-  <si>
-    <t>幽灵时装包</t>
-  </si>
-  <si>
-    <t>兑换圣战时装包*1</t>
-  </si>
-  <si>
-    <t>圣战时装包</t>
-  </si>
-  <si>
-    <t>兑换法神时装包*1</t>
-  </si>
-  <si>
-    <t>法神时装包</t>
-  </si>
-  <si>
-    <t>兑换天尊时装包*1</t>
-  </si>
-  <si>
-    <t>天尊时装包</t>
+    <t>兑换斩仙时装包*1</t>
+  </si>
+  <si>
+    <t>斩仙时装包</t>
+  </si>
+  <si>
+    <t>兑换魔尊时装包*1</t>
+  </si>
+  <si>
+    <t>魔尊时装包</t>
+  </si>
+  <si>
+    <t>兑换幽冥时装包*1</t>
+  </si>
+  <si>
+    <t>幽冥时装包</t>
+  </si>
+  <si>
+    <t>兑换战魂时装包*1</t>
+  </si>
+  <si>
+    <t>战魂时装包</t>
+  </si>
+  <si>
+    <t>兑换法魂时装包*1</t>
+  </si>
+  <si>
+    <t>法魂时装包</t>
+  </si>
+  <si>
+    <t>兑换道魂时装包*1</t>
+  </si>
+  <si>
+    <t>道魂时装包</t>
   </si>
   <si>
     <t>兑换图鉴龙之力*1</t>

--- a/Excel/SevenDayConfig.xlsx
+++ b/Excel/SevenDayConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="70">
   <si>
     <t>#</t>
   </si>
@@ -231,6 +231,12 @@
   </si>
   <si>
     <t>高级书页</t>
+  </si>
+  <si>
+    <t>兑换橙宠自选</t>
+  </si>
+  <si>
+    <t>橙宠自选</t>
   </si>
 </sst>
 </file>
@@ -1233,15 +1239,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L70"/>
+  <dimension ref="C1:L71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.2545454545455" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.2583333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1272727272727" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.8727272727273" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.875" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
@@ -3051,6 +3057,35 @@
       </c>
       <c r="K70" s="1">
         <v>20</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C71" s="1">
+        <v>609</v>
+      </c>
+      <c r="D71" s="1">
+        <v>7</v>
+      </c>
+      <c r="E71" s="1">
+        <v>100000</v>
+      </c>
+      <c r="F71" s="1">
+        <v>1</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I71" s="1">
+        <v>4</v>
+      </c>
+      <c r="J71" s="1">
+        <v>201</v>
+      </c>
+      <c r="K71" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/SevenDayConfig.xlsx
+++ b/Excel/SevenDayConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -1243,11 +1243,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.2583333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.2545454545455" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1272727272727" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.8727272727273" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
@@ -3067,7 +3067,7 @@
         <v>7</v>
       </c>
       <c r="E71" s="1">
-        <v>100000</v>
+        <v>388888</v>
       </c>
       <c r="F71" s="1">
         <v>1</v>

--- a/Excel/SevenDayConfig.xlsx
+++ b/Excel/SevenDayConfig.xlsx
@@ -3067,7 +3067,7 @@
         <v>7</v>
       </c>
       <c r="E71" s="1">
-        <v>388888</v>
+        <v>188888</v>
       </c>
       <c r="F71" s="1">
         <v>1</v>

--- a/Excel/SevenDayConfig.xlsx
+++ b/Excel/SevenDayConfig.xlsx
@@ -209,10 +209,10 @@
     <t>神技自选</t>
   </si>
   <si>
-    <t>兑换法宝自选*1</t>
-  </si>
-  <si>
-    <t>法宝自选</t>
+    <t>兑换新手法宝自选*1</t>
+  </si>
+  <si>
+    <t>新手法宝自选</t>
   </si>
   <si>
     <t>兑换传世挑战卷*4</t>
@@ -2647,7 +2647,7 @@
         <v>4</v>
       </c>
       <c r="J55" s="1">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K55" s="1">
         <v>1</v>

--- a/Excel/SevenDayConfig.xlsx
+++ b/Excel/SevenDayConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -1243,13 +1243,13 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.2545454545455" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.2566371681416" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1272727272727" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.8727272727273" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.5044247787611" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1238938053097" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.8761061946903" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.50442477876106" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5044247787611" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2284,7 +2284,7 @@
         <v>4</v>
       </c>
       <c r="E41" s="1">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="F41" s="1">
         <v>10</v>
@@ -2458,7 +2458,7 @@
         <v>5</v>
       </c>
       <c r="E48" s="1">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F48" s="1">
         <v>5</v>
@@ -2632,7 +2632,7 @@
         <v>6</v>
       </c>
       <c r="E55" s="1">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="F55" s="1">
         <v>3</v>
@@ -2835,7 +2835,7 @@
         <v>7</v>
       </c>
       <c r="E63" s="1">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="F63" s="1">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         <v>7</v>
       </c>
       <c r="E71" s="1">
-        <v>188888</v>
+        <v>66666</v>
       </c>
       <c r="F71" s="1">
         <v>1</v>

--- a/Excel/SevenDayConfig.xlsx
+++ b/Excel/SevenDayConfig.xlsx
@@ -1527,7 +1527,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F12" s="1">
         <v>10</v>
@@ -1672,7 +1672,7 @@
         <v>2</v>
       </c>
       <c r="E18" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F18" s="1">
         <v>40</v>
@@ -1701,7 +1701,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F19" s="1">
         <v>40</v>
@@ -1730,7 +1730,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F20" s="1">
         <v>40</v>
@@ -1759,7 +1759,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F21" s="1">
         <v>40</v>
@@ -1788,7 +1788,7 @@
         <v>2</v>
       </c>
       <c r="E22" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F22" s="1">
         <v>40</v>
@@ -1817,7 +1817,7 @@
         <v>2</v>
       </c>
       <c r="E23" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F23" s="1">
         <v>40</v>
@@ -1846,7 +1846,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F24" s="1">
         <v>15</v>
@@ -1933,7 +1933,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F27" s="1">
         <v>15</v>
@@ -1994,7 +1994,7 @@
         <v>3</v>
       </c>
       <c r="E30" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F30" s="1">
         <v>40</v>
@@ -2023,7 +2023,7 @@
         <v>3</v>
       </c>
       <c r="E31" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F31" s="1">
         <v>40</v>
@@ -2052,7 +2052,7 @@
         <v>3</v>
       </c>
       <c r="E32" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F32" s="1">
         <v>40</v>
@@ -2081,7 +2081,7 @@
         <v>3</v>
       </c>
       <c r="E33" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F33" s="1">
         <v>40</v>
@@ -2110,7 +2110,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F34" s="1">
         <v>40</v>
@@ -2139,7 +2139,7 @@
         <v>3</v>
       </c>
       <c r="E35" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F35" s="1">
         <v>20</v>
@@ -2226,7 +2226,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F38" s="1">
         <v>20</v>
@@ -2313,7 +2313,7 @@
         <v>4</v>
       </c>
       <c r="E42" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F42" s="1">
         <v>25</v>
@@ -2400,7 +2400,7 @@
         <v>4</v>
       </c>
       <c r="E45" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F45" s="1">
         <v>25</v>
@@ -2487,7 +2487,7 @@
         <v>5</v>
       </c>
       <c r="E49" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F49" s="1">
         <v>30</v>
@@ -2574,7 +2574,7 @@
         <v>5</v>
       </c>
       <c r="E52" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F52" s="1">
         <v>30</v>
@@ -2661,7 +2661,7 @@
         <v>6</v>
       </c>
       <c r="E56" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F56" s="1">
         <v>35</v>
@@ -2748,7 +2748,7 @@
         <v>6</v>
       </c>
       <c r="E59" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F59" s="1">
         <v>35</v>
@@ -2864,7 +2864,7 @@
         <v>7</v>
       </c>
       <c r="E64" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F64" s="1">
         <v>50</v>
@@ -2951,7 +2951,7 @@
         <v>7</v>
       </c>
       <c r="E67" s="1">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F67" s="1">
         <v>50</v>

--- a/Excel/SevenDayConfig.xlsx
+++ b/Excel/SevenDayConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -1243,22 +1243,22 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="11.2566371681416" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.2545454545455" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5044247787611" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1238938053097" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.8761061946903" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.50442477876106" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5044247787611" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1272727272727" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.8727272727273" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="12:12">
+    <row r="1" customHeight="1" spans="3:12">
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1345,7 +1345,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:11">
+    <row r="6" customHeight="1" spans="3:12">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:11">
+    <row r="7" customHeight="1" spans="3:12">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:11">
+    <row r="8" customHeight="1" spans="3:12">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:11">
+    <row r="14" customHeight="1" spans="3:12">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:11">
+    <row r="15" customHeight="1" spans="3:12">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1635,7 +1635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="10:10">
+    <row r="29" customHeight="1" spans="3:11">
       <c r="J29" s="4"/>
     </row>
     <row r="30" customHeight="1" spans="3:11">
@@ -3009,7 +3009,7 @@
         <v>7</v>
       </c>
       <c r="E69" s="1">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="F69" s="1">
         <v>100</v>
@@ -3038,7 +3038,7 @@
         <v>7</v>
       </c>
       <c r="E70" s="1">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="F70" s="1">
         <v>40</v>

--- a/Excel/SevenDayConfig.xlsx
+++ b/Excel/SevenDayConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="72">
   <si>
     <t>#</t>
   </si>
@@ -237,6 +237,12 @@
   </si>
   <si>
     <t>橙宠自选</t>
+  </si>
+  <si>
+    <t>兑换红宠自选</t>
+  </si>
+  <si>
+    <t>红宠自选</t>
   </si>
 </sst>
 </file>
@@ -1239,7 +1245,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L71"/>
+  <dimension ref="C1:L72"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -3088,6 +3094,35 @@
         <v>1</v>
       </c>
     </row>
+    <row r="72" customHeight="1" spans="3:11">
+      <c r="C72" s="1">
+        <v>610</v>
+      </c>
+      <c r="D72" s="1">
+        <v>7</v>
+      </c>
+      <c r="E72" s="1">
+        <v>188888</v>
+      </c>
+      <c r="F72" s="1">
+        <v>1</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I72" s="1">
+        <v>4</v>
+      </c>
+      <c r="J72" s="1">
+        <v>204</v>
+      </c>
+      <c r="K72" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:G5" errorStyle="warning">
